--- a/My_Professional_Reviews/UAS-5_Skor.xlsx
+++ b/My_Professional_Reviews/UAS-5_Skor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raihaan\AppData\Local\Packages\5319275A.WhatsAppDesktop_cv1g1gvanyjgm\LocalState\sessions\7014A7E93CCFA39587CCAB38745BCE43FF06A6D9\transfers\2025-52\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raihaan\all-about-me\My_Professional_Reviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631A70FA-4E96-4B81-B4B7-54C026168D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A78F5A-1282-447B-AF84-C62286DDEA0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -121,14 +121,30 @@
   <si>
     <t>Muhammad Raihaan Perdana</t>
   </si>
+  <si>
+    <t>Arlow Emmanuel Hergara</t>
+  </si>
+  <si>
+    <t>Rifki Friz Farabi</t>
+  </si>
+  <si>
+    <t>Sebastian Enrico Nathanael</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -164,8 +180,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF343A40"/>
+      <name val="Source Sans Pro"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,8 +200,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -187,18 +215,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFD6D8D9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD6D8D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,9 +687,27 @@
       <c r="AP3" s="4"/>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A4" s="6">
+        <v>13523161</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="7">
+        <f>AVERAGE(C4:F4)</f>
+        <v>4.5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -655,10 +717,28 @@
       <c r="AK4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="5" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>11422030</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4">
+        <f>IF(COUNT(C5:F5)=0,"",AVERAGE(C5:F5))</f>
+        <v>4.75</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -668,10 +748,28 @@
       <c r="AK5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="6" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>13523134</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f>AVERAGE(C6:F6)</f>
+        <v>5</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -1811,9 +1909,27 @@
       <c r="AP3" s="4"/>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A4" s="6">
+        <v>13523161</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4">
+        <f>AVERAGE(C4:F4)</f>
+        <v>5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -1823,10 +1939,28 @@
       <c r="AK4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="5" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>11422030</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" ref="G5:G6" si="1">IF(COUNT(C5:F5)=0,"",AVERAGE(C5:F5))</f>
+        <v>4.75</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -1836,10 +1970,28 @@
       <c r="AK5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="6" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>13523134</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f>AVERAGE(C6:F6)</f>
+        <v>4.5</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -2631,7 +2783,7 @@
     </row>
     <row r="67" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G67" s="4" t="str">
-        <f t="shared" ref="G67:G82" si="1">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
+        <f t="shared" ref="G67:G82" si="2">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
         <v/>
       </c>
       <c r="L67" s="4"/>
@@ -2644,7 +2796,7 @@
     </row>
     <row r="68" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G68" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L68" s="4"/>
@@ -2657,7 +2809,7 @@
     </row>
     <row r="69" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G69" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L69" s="4"/>
@@ -2670,7 +2822,7 @@
     </row>
     <row r="70" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G70" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L70" s="4"/>
@@ -2683,7 +2835,7 @@
     </row>
     <row r="71" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G71" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L71" s="4"/>
@@ -2696,7 +2848,7 @@
     </row>
     <row r="72" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G72" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L72" s="4"/>
@@ -2709,7 +2861,7 @@
     </row>
     <row r="73" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G73" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L73" s="4"/>
@@ -2722,7 +2874,7 @@
     </row>
     <row r="74" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G74" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L74" s="4"/>
@@ -2735,7 +2887,7 @@
     </row>
     <row r="75" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G75" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L75" s="4"/>
@@ -2748,7 +2900,7 @@
     </row>
     <row r="76" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G76" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L76" s="4"/>
@@ -2761,7 +2913,7 @@
     </row>
     <row r="77" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G77" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L77" s="4"/>
@@ -2774,7 +2926,7 @@
     </row>
     <row r="78" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G78" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L78" s="4"/>
@@ -2787,7 +2939,7 @@
     </row>
     <row r="79" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G79" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L79" s="4"/>
@@ -2800,7 +2952,7 @@
     </row>
     <row r="80" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G80" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L80" s="4"/>
@@ -2813,7 +2965,7 @@
     </row>
     <row r="81" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G81" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L81" s="4"/>
@@ -2826,7 +2978,7 @@
     </row>
     <row r="82" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G82" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L82" s="4"/>
@@ -2979,9 +3131,27 @@
       <c r="AP3" s="4"/>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A4" s="6">
+        <v>13523161</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4">
+        <f>AVERAGE(C4:F4)</f>
+        <v>4.75</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -2991,10 +3161,28 @@
       <c r="AK4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="5" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>11422030</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" ref="G5:G6" si="1">IF(COUNT(C5:F5)=0,"",AVERAGE(C5:F5))</f>
+        <v>4.5</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -3004,10 +3192,28 @@
       <c r="AK5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="6" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>13523134</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f>AVERAGE(C6:F6)</f>
+        <v>4.75</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -3799,7 +4005,7 @@
     </row>
     <row r="67" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G67" s="4" t="str">
-        <f t="shared" ref="G67:G82" si="1">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
+        <f t="shared" ref="G67:G82" si="2">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
         <v/>
       </c>
       <c r="L67" s="4"/>
@@ -3812,7 +4018,7 @@
     </row>
     <row r="68" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G68" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L68" s="4"/>
@@ -3825,7 +4031,7 @@
     </row>
     <row r="69" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G69" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L69" s="4"/>
@@ -3838,7 +4044,7 @@
     </row>
     <row r="70" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G70" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L70" s="4"/>
@@ -3851,7 +4057,7 @@
     </row>
     <row r="71" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G71" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L71" s="4"/>
@@ -3864,7 +4070,7 @@
     </row>
     <row r="72" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G72" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L72" s="4"/>
@@ -3877,7 +4083,7 @@
     </row>
     <row r="73" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G73" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L73" s="4"/>
@@ -3890,7 +4096,7 @@
     </row>
     <row r="74" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G74" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L74" s="4"/>
@@ -3903,7 +4109,7 @@
     </row>
     <row r="75" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G75" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L75" s="4"/>
@@ -3916,7 +4122,7 @@
     </row>
     <row r="76" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G76" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L76" s="4"/>
@@ -3929,7 +4135,7 @@
     </row>
     <row r="77" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G77" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L77" s="4"/>
@@ -3942,7 +4148,7 @@
     </row>
     <row r="78" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G78" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L78" s="4"/>
@@ -3955,7 +4161,7 @@
     </row>
     <row r="79" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G79" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L79" s="4"/>
@@ -3968,7 +4174,7 @@
     </row>
     <row r="80" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G80" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L80" s="4"/>
@@ -3981,7 +4187,7 @@
     </row>
     <row r="81" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G81" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L81" s="4"/>
@@ -3994,7 +4200,7 @@
     </row>
     <row r="82" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G82" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L82" s="4"/>
@@ -4147,9 +4353,27 @@
       <c r="AP3" s="4"/>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A4" s="6">
+        <v>13523161</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4">
+        <f>AVERAGE(C4:F4)</f>
+        <v>4.75</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -4159,10 +4383,28 @@
       <c r="AK4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="5" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>11422030</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" ref="G5:G6" si="1">IF(COUNT(C5:F5)=0,"",AVERAGE(C5:F5))</f>
+        <v>4.75</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -4172,10 +4414,28 @@
       <c r="AK5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="6" spans="1:42" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>13523134</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f>AVERAGE(C6:F6)</f>
+        <v>4.75</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -4967,7 +5227,7 @@
     </row>
     <row r="67" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G67" s="4" t="str">
-        <f t="shared" ref="G67:G82" si="1">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
+        <f t="shared" ref="G67:G82" si="2">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
         <v/>
       </c>
       <c r="L67" s="4"/>
@@ -4980,7 +5240,7 @@
     </row>
     <row r="68" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G68" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L68" s="4"/>
@@ -4993,7 +5253,7 @@
     </row>
     <row r="69" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G69" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L69" s="4"/>
@@ -5006,7 +5266,7 @@
     </row>
     <row r="70" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G70" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L70" s="4"/>
@@ -5019,7 +5279,7 @@
     </row>
     <row r="71" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G71" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L71" s="4"/>
@@ -5032,7 +5292,7 @@
     </row>
     <row r="72" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G72" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L72" s="4"/>
@@ -5045,7 +5305,7 @@
     </row>
     <row r="73" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G73" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L73" s="4"/>
@@ -5058,7 +5318,7 @@
     </row>
     <row r="74" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G74" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L74" s="4"/>
@@ -5071,7 +5331,7 @@
     </row>
     <row r="75" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G75" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L75" s="4"/>
@@ -5084,7 +5344,7 @@
     </row>
     <row r="76" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G76" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L76" s="4"/>
@@ -5097,7 +5357,7 @@
     </row>
     <row r="77" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G77" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L77" s="4"/>
@@ -5110,7 +5370,7 @@
     </row>
     <row r="78" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G78" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L78" s="4"/>
@@ -5123,7 +5383,7 @@
     </row>
     <row r="79" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G79" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L79" s="4"/>
@@ -5136,7 +5396,7 @@
     </row>
     <row r="80" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G80" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L80" s="4"/>
@@ -5149,7 +5409,7 @@
     </row>
     <row r="81" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G81" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L81" s="4"/>
@@ -5162,7 +5422,7 @@
     </row>
     <row r="82" spans="7:42" x14ac:dyDescent="0.3">
       <c r="G82" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="L82" s="4"/>
